--- a/hourly datasets/cap_gen_year11final.xlsx
+++ b/hourly datasets/cap_gen_year11final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1095408508766886</v>
+        <v>0.1088487119887804</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09923718903447988</v>
+        <v>0.09788854284988854</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2087780399111685</v>
+        <v>0.2067372548386689</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08293037643502431</v>
+        <v>0.07898379826169051</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1924712273117129</v>
+        <v>0.1878325102504709</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08664581060446666</v>
+        <v>0.08395904872941672</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1961866614811553</v>
+        <v>0.1928077607181971</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08809867114853734</v>
+        <v>0.07997276881664886</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1976395220252259</v>
+        <v>0.1888214808054292</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08783588393753544</v>
+        <v>0.07912378822443203</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006160670765040378</v>
+        <v>0.005376763064540695</v>
       </c>
       <c r="D7" t="n">
-        <v>5.923068308793769</v>
+        <v>5.507631184603765</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01595706240556712</v>
+        <v>0.005404812904932825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07575650494330734</v>
+        <v>0.06858101155993032</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09991526293176362</v>
+        <v>0.08966656488893418</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1973767348142241</v>
+        <v>0.1879725002132124</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0157241038097211</v>
+        <v>0.005095130053103908</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001721439986165525</v>
+        <v>0.0007719307051892559</v>
       </c>
       <c r="D8" t="n">
-        <v>1.250819828511136</v>
+        <v>0.747800169084272</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01094147031537767</v>
+        <v>0.004415815177789496</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01234771130724778</v>
+        <v>0.003580147800228701</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01910049631219455</v>
+        <v>0.006610112305979273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1252649546864097</v>
+        <v>0.1139438420418843</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01208892776099924</v>
+        <v>0.006310466506383646</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001840075054147123</v>
+        <v>0.000985132569069246</v>
       </c>
       <c r="D9" t="n">
-        <v>0.87551099422637</v>
+        <v>0.5808103582355933</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009477498262888963</v>
+        <v>0.004958104196301456</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008479945585292482</v>
+        <v>0.004377585438052683</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01569790993670598</v>
+        <v>0.008243347574714548</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1216297786376879</v>
+        <v>0.115159178495164</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01380883928723627</v>
+        <v>0.004700742038803388</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001659177192505468</v>
+        <v>0.0007997862729733581</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8671545001381232</v>
+        <v>0.379592119335375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01561553626919321</v>
+        <v>0.00581567153157731</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01055572963197893</v>
+        <v>0.003132223237340957</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01706194894249302</v>
+        <v>0.006269260840265686</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1233496901639249</v>
+        <v>0.1135494540275837</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03167191081166314</v>
+        <v>0.02915457565326442</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1412127616883518</v>
+        <v>0.1380032876420448</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05210666110496477</v>
+        <v>0.04879840641939123</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1616475119816534</v>
+        <v>0.1576471184081716</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06291557863752552</v>
+        <v>0.05979957199208642</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1724564295142141</v>
+        <v>0.1686482839808668</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07365463933776871</v>
+        <v>0.06905533374517989</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1831954902144573</v>
+        <v>0.1779040457339602</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07972835105340612</v>
+        <v>0.07462046271751517</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1892692019300947</v>
+        <v>0.1834691747062955</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08101929742172134</v>
+        <v>0.07634107129776729</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1905601482984099</v>
+        <v>0.1851897832865476</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08334608047783983</v>
+        <v>0.07932978003631712</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1928869313545284</v>
+        <v>0.1881784920250975</v>
       </c>
     </row>
     <row r="18">
@@ -805,13 +805,23 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1095408508766886</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>-0.1088487119887804</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.009653135095993222</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-21.08086096939171</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.03328539094222872</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.1278125131761482</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.08988491080141235</v>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -823,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08588987266372432</v>
+        <v>0.08053969351228982</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1954307235404129</v>
+        <v>0.1893884055010702</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08952242401224325</v>
+        <v>0.0850955297325737</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -849,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1990632748889319</v>
+        <v>0.193944241721354</v>
       </c>
     </row>
     <row r="21">
@@ -859,7 +869,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09089316000939306</v>
+        <v>0.08755877513168771</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -867,7 +877,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2004340108860817</v>
+        <v>0.1964074871204681</v>
       </c>
     </row>
     <row r="22">
@@ -877,25 +887,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09475971894242061</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.007620871415397229</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1009979561198.836</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.04347295510024996</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.07975882774137004</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1097606101434712</v>
-      </c>
+        <v>0.09200834544471909</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2043005698191092</v>
+        <v>0.2008570574334994</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09704936308425112</v>
+        <v>0.09381522371964594</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +913,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2065902139609397</v>
+        <v>0.2026639357084263</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1001725386056939</v>
+        <v>0.09759923631297386</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007814031344815753</v>
+        <v>0.007515865121047314</v>
       </c>
       <c r="D24" t="n">
-        <v>996697712547.6837</v>
+        <v>984735939167.6863</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05782375755067647</v>
+        <v>0.05559700854958977</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08481222431341105</v>
+        <v>0.08283354265384828</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1155328528979767</v>
+        <v>0.1123649299720995</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2097133894823825</v>
+        <v>0.2064479483017542</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1021566949567594</v>
+        <v>0.0987141370624781</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007892856342740262</v>
+        <v>0.007406468849871225</v>
       </c>
       <c r="D25" t="n">
-        <v>603442959324.0503</v>
+        <v>598353211218.308</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05376238981176969</v>
+        <v>0.0518879732350751</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08662495127093868</v>
+        <v>0.08416519206076789</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1176884386425802</v>
+        <v>0.1132630820641883</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2116975458334481</v>
+        <v>0.2075628490512584</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1012313291632006</v>
+        <v>0.09927167488190149</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008015375722886199</v>
+        <v>0.007602921815980755</v>
       </c>
       <c r="D26" t="n">
-        <v>22.82675888221823</v>
+        <v>22.91198768207986</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05990244578407614</v>
+        <v>0.05837883153977028</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08547361794743422</v>
+        <v>0.08433523389667742</v>
       </c>
       <c r="G26" t="n">
-        <v>0.116989040378967</v>
+        <v>0.114208115867125</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2107721800398892</v>
+        <v>0.2081203868706819</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1007,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1076876494503328</v>
+        <v>0.1051458499092676</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008049226972368427</v>
+        <v>0.007466626163582817</v>
       </c>
       <c r="D27" t="n">
-        <v>22.76106326311974</v>
+        <v>23.04462645421248</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06557252171094248</v>
+        <v>0.05986972624477492</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09185393207197737</v>
+        <v>0.0904856587043814</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1235213668286879</v>
+        <v>0.119806041114153</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2172285003270214</v>
+        <v>0.213994561898048</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1076451618059842</v>
+        <v>0.1042666036748791</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008220632994280091</v>
+        <v>0.007786385731462401</v>
       </c>
       <c r="D28" t="n">
-        <v>951876673633.943</v>
+        <v>944327676460.796</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09908224531215967</v>
+        <v>0.08906646418049928</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09149338219573487</v>
+        <v>0.08897840550379167</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1237969414162337</v>
+        <v>0.1195548018459666</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2171860126826728</v>
+        <v>0.2131153156636595</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1063,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0177844887245429</v>
+        <v>0.005020305436578113</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001713823760253659</v>
+        <v>0.0007257843598062779</v>
       </c>
       <c r="D29" t="n">
-        <v>1.717639576708349</v>
+        <v>0.6810691676762491</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0102958081672072</v>
+        <v>0.006027340469593796</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01438747950771367</v>
+        <v>0.003596708740604919</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02118149794137169</v>
+        <v>0.006443902132551152</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1273253396012315</v>
+        <v>0.1138690174253585</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year11final.xlsx
+++ b/hourly datasets/cap_gen_year11final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2346383703477429</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1088487119887804</v>
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1050060637103075</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09788854284988854</v>
+        <v>0.3756494384605032</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2067372548386689</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2460171318230679</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07898379826169051</v>
+        <v>0.3878755300632665</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1878325102504709</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2582432234258312</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08395904872941672</v>
+        <v>0.4361062526826056</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1928077607181971</v>
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3064739460451702</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07997276881664886</v>
+        <v>0.464959559293845</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1888214808054292</v>
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3353272526564096</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07912378822443203</v>
+        <v>0.4722308333780022</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005376763064540695</v>
+        <v>0.01510623214355096</v>
       </c>
       <c r="D7" t="n">
-        <v>5.507631184603765</v>
+        <v>16.22249078821915</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005404812904932825</v>
+        <v>0.006104148939335458</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06858101155993032</v>
+        <v>0.2221375215535374</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08966656488893418</v>
+        <v>0.2813709048658219</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1879725002132124</v>
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3425985267405668</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005095130053103908</v>
+        <v>0.5261546809365952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007719307051892559</v>
+        <v>0.009218992026450538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.747800169084272</v>
+        <v>5.867905501012027</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004415815177789496</v>
+        <v>0.006098998158160457</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003580147800228701</v>
+        <v>0.03521065216696706</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006610112305979273</v>
+        <v>0.07143049778740149</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1139438420418843</v>
+        <v>136</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3965223742991598</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006310466506383646</v>
+        <v>0.5320889674472963</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000985132569069246</v>
+        <v>0.01266248868411183</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5808103582355933</v>
+        <v>4.691586256782892</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004958104196301456</v>
+        <v>0.007009638085502765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004377585438052683</v>
+        <v>0.03532318490557448</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008243347574714548</v>
+        <v>0.08507210950682136</v>
       </c>
       <c r="H9" t="n">
-        <v>0.115159178495164</v>
+        <v>136</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4024566608098609</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004700742038803388</v>
+        <v>0.5060940364633887</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0007997862729733581</v>
+        <v>0.01559782905412169</v>
       </c>
       <c r="D10" t="n">
-        <v>0.379592119335375</v>
+        <v>14.22444405243868</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00581567153157731</v>
+        <v>0.008449759423168253</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003132223237340957</v>
+        <v>0.1997252295259587</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006269260840265686</v>
+        <v>0.2608780962640955</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1135494540275837</v>
+        <v>163</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3764617298259533</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02915457565326442</v>
+        <v>0.2735911493655021</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1380032876420448</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1439588427280667</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04879840641939123</v>
+        <v>0.2972123933101984</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1576471184081716</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.167580086672763</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05979957199208642</v>
+        <v>0.3115748775559326</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1686482839808668</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1819425709184972</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06905533374517989</v>
+        <v>0.3205994893367494</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1779040457339602</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.190967182699314</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07462046271751517</v>
+        <v>0.3272690968428532</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1834691747062955</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1976367902054178</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07634107129776729</v>
+        <v>0.3320516546206974</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1851897832865476</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.202419347983262</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07932978003631712</v>
+        <v>0.3356805541919458</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1881784920250975</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2060482475545104</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1088487119887804</v>
+        <v>0.1296323066374354</v>
       </c>
       <c r="C18" t="n">
-        <v>0.009653135095993222</v>
+        <v>0.009660572025959319</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.08086096939171</v>
+        <v>-21.09710200249602</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03328539094222872</v>
+        <v>0.03331103454079746</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1278125131761482</v>
+        <v>-0.1279109819844503</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08988491080141235</v>
+        <v>-0.0899541595770683</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08053969351228982</v>
+        <v>0.3383973430897798</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1893884055010702</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2087650364523444</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0850955297325737</v>
+        <v>0.3428899830915119</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.193944241721354</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2132576764540765</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +931,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08755877513168771</v>
+        <v>0.3451511335421492</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +939,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1964074871204681</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2155188269047138</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +952,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09200834544471909</v>
+        <v>0.3497579571431919</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +960,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2008570574334994</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2201256505057565</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +973,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09381522371964594</v>
+        <v>0.3555232315526753</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +981,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2026639357084263</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2258909249152399</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +994,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09759923631297386</v>
+        <v>0.3607998356575213</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007515865121047314</v>
+        <v>0.007503379730738145</v>
       </c>
       <c r="D24" t="n">
-        <v>984735939167.6863</v>
+        <v>984589021176.2227</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05559700854958977</v>
+        <v>0.05547189618339977</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08283354265384828</v>
+        <v>0.08269771988031656</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1123649299720995</v>
+        <v>0.1121800865579387</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2064479483017542</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2311675290200859</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +1025,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0987141370624781</v>
+        <v>0.3648972647872635</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007406468849871225</v>
+        <v>0.007355999466617352</v>
       </c>
       <c r="D25" t="n">
-        <v>598353211218.308</v>
+        <v>598247641883.7943</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0518879732350751</v>
+        <v>0.05071049976663321</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08416519206076789</v>
+        <v>0.0841030561992042</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1132630820641883</v>
+        <v>0.1130029163794312</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2075628490512584</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2352649581498281</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +1056,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09927167488190149</v>
+        <v>0.3675695439484468</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007602921815980755</v>
+        <v>0.00750295851391825</v>
       </c>
       <c r="D26" t="n">
-        <v>22.91198768207986</v>
+        <v>22.86717722090458</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05837883153977028</v>
+        <v>0.05562340254001864</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08433523389667742</v>
+        <v>0.0842798852051613</v>
       </c>
       <c r="G26" t="n">
-        <v>0.114208115867125</v>
+        <v>0.1137605388218032</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2081203868706819</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2379372373110114</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1087,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1051458499092676</v>
+        <v>0.3748729356723043</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007466626163582817</v>
+        <v>0.007393669355374071</v>
       </c>
       <c r="D27" t="n">
-        <v>23.04462645421248</v>
+        <v>22.96832808100905</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05986972624477492</v>
+        <v>0.05902293590377569</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0904856587043814</v>
+        <v>0.09013705496607527</v>
       </c>
       <c r="G27" t="n">
-        <v>0.119806041114153</v>
+        <v>0.1191710899707612</v>
       </c>
       <c r="H27" t="n">
-        <v>0.213994561898048</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2452406290348689</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1118,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1042666036748791</v>
+        <v>0.3781809863020896</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007786385731462401</v>
+        <v>0.007591140348086227</v>
       </c>
       <c r="D28" t="n">
-        <v>944327676460.796</v>
+        <v>944053925554.832</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08906646418049928</v>
+        <v>0.08586069962518712</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08897840550379167</v>
+        <v>0.0886295696397644</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1195548018459666</v>
+        <v>0.1184395765362787</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2131153156636595</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2485486796646542</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1149,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005020305436578113</v>
+        <v>0.3373148324483354</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0007257843598062779</v>
+        <v>0.005076399115065904</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6810691676762491</v>
+        <v>6.94450804901352</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006027340469593796</v>
+        <v>0.007839457650949929</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003596708740604919</v>
+        <v>0.02563679296429852</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006443902132551152</v>
+        <v>0.04554880728322604</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1138690174253585</v>
+        <v>114</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2076825258109</v>
       </c>
     </row>
   </sheetData>
